--- a/intermediate/dashboard_output_ghggdp.xlsx
+++ b/intermediate/dashboard_output_ghggdp.xlsx
@@ -486,11 +486,17 @@
           <t>AFG</t>
         </is>
       </c>
+      <c r="H3">
+        <v>-1.25</v>
+      </c>
       <c r="I3">
         <v>2023</v>
       </c>
       <c r="J3">
-        <v>0.4182956789194352</v>
+        <v>0.4</v>
+      </c>
+      <c r="K3">
+        <v>0.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -501,6 +507,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N3">
+        <v>2015</v>
       </c>
     </row>
     <row r="4">
@@ -631,10 +640,10 @@
         </is>
       </c>
       <c r="H7">
-        <v>-1.428571428571429</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J7">
         <v>0.5</v>
@@ -655,6 +664,9 @@
       <c r="N7">
         <v>2015</v>
       </c>
+      <c r="O7">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -675,11 +687,17 @@
           <t>ARG</t>
         </is>
       </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
       <c r="I8">
         <v>2024</v>
       </c>
       <c r="J8">
-        <v>0.3114332786057337</v>
+        <v>0.3</v>
+      </c>
+      <c r="K8">
+        <v>0.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -690,6 +708,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N8">
+        <v>2015</v>
       </c>
     </row>
     <row r="9">
@@ -747,11 +768,17 @@
           <t>ATG</t>
         </is>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
       <c r="I10">
         <v>2024</v>
       </c>
       <c r="J10">
-        <v>0.2668615452790046</v>
+        <v>0.3</v>
+      </c>
+      <c r="K10">
+        <v>0.3</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -762,6 +789,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N10">
+        <v>2015</v>
       </c>
     </row>
     <row r="11">
@@ -784,10 +814,10 @@
         </is>
       </c>
       <c r="H11">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I11">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J11">
         <v>0.4</v>
@@ -809,7 +839,7 @@
         <v>2015</v>
       </c>
       <c r="O11">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="12">
@@ -867,11 +897,17 @@
           <t>AZE</t>
         </is>
       </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
       <c r="I13">
         <v>2024</v>
       </c>
       <c r="J13">
-        <v>0.255533114981604</v>
+        <v>0.3</v>
+      </c>
+      <c r="K13">
+        <v>0.3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -882,6 +918,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N13">
+        <v>2015</v>
       </c>
     </row>
     <row r="14">
@@ -907,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J14">
         <v>0.5</v>
@@ -929,7 +968,7 @@
         <v>2015</v>
       </c>
       <c r="O14">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15">
@@ -991,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J16">
         <v>0.4</v>
@@ -1012,6 +1051,9 @@
       <c r="N16">
         <v>2015</v>
       </c>
+      <c r="O16">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1033,10 +1075,10 @@
         </is>
       </c>
       <c r="H17">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I17">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J17">
         <v>0.7000000000000001</v>
@@ -1058,7 +1100,7 @@
         <v>2015</v>
       </c>
       <c r="O17">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1153,10 +1195,10 @@
         </is>
       </c>
       <c r="H20">
-        <v>2.857142857142857</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="I20">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J20">
         <v>0.6000000000000001</v>
@@ -1178,7 +1220,7 @@
         <v>2015</v>
       </c>
       <c r="O20">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1240,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J22">
         <v>0.5</v>
@@ -1262,7 +1304,7 @@
         <v>2015</v>
       </c>
       <c r="O22">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="23">
@@ -1285,13 +1327,13 @@
         </is>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I23">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J23">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K23">
         <v>0.4</v>
@@ -1309,6 +1351,9 @@
       <c r="N23">
         <v>2015</v>
       </c>
+      <c r="O23">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1329,11 +1374,17 @@
           <t>BLZ</t>
         </is>
       </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
       <c r="I24">
         <v>2024</v>
       </c>
       <c r="J24">
-        <v>0.2792534115255282</v>
+        <v>0.3</v>
+      </c>
+      <c r="K24">
+        <v>0.3</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1344,6 +1395,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N24">
+        <v>2015</v>
       </c>
     </row>
     <row r="25">
@@ -1366,13 +1420,13 @@
         </is>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I25">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J25">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K25">
         <v>0.4</v>
@@ -1390,6 +1444,9 @@
       <c r="N25">
         <v>2015</v>
       </c>
+      <c r="O25">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1410,11 +1467,17 @@
           <t>BRA</t>
         </is>
       </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
       <c r="I26">
         <v>2024</v>
       </c>
       <c r="J26">
-        <v>0.3072289944120202</v>
+        <v>0.3</v>
+      </c>
+      <c r="K26">
+        <v>0.3</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1425,6 +1488,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N26">
+        <v>2015</v>
       </c>
     </row>
     <row r="27">
@@ -1482,11 +1548,17 @@
           <t>BRN</t>
         </is>
       </c>
+      <c r="H28">
+        <v>-1.111111111111111</v>
+      </c>
       <c r="I28">
         <v>2024</v>
       </c>
       <c r="J28">
-        <v>0.3799044066020743</v>
+        <v>0.4</v>
+      </c>
+      <c r="K28">
+        <v>0.3</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1497,6 +1569,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N28">
+        <v>2015</v>
       </c>
     </row>
     <row r="29">
@@ -1555,13 +1630,13 @@
         </is>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>-2.222222222222222</v>
       </c>
       <c r="I30">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J30">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K30">
         <v>0.4</v>
@@ -1579,6 +1654,9 @@
       <c r="N30">
         <v>2015</v>
       </c>
+      <c r="O30">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1600,13 +1678,13 @@
         </is>
       </c>
       <c r="H31">
-        <v>0.6789638932496074</v>
+        <v>0.4222629222629226</v>
       </c>
       <c r="I31">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="K31">
         <v>4.600000000000001</v>
@@ -1625,7 +1703,7 @@
         <v>2015</v>
       </c>
       <c r="O31">
-        <v>3.757092907092897</v>
+        <v>3.536097236097248</v>
       </c>
     </row>
     <row r="32">
@@ -1647,11 +1725,17 @@
           <t>CAN</t>
         </is>
       </c>
+      <c r="H32">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I32">
         <v>2024</v>
       </c>
       <c r="J32">
-        <v>0.3429965511303308</v>
+        <v>0.3</v>
+      </c>
+      <c r="K32">
+        <v>0.4</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1662,6 +1746,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N32">
+        <v>2015</v>
+      </c>
+      <c r="O32">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1756,13 +1846,13 @@
         </is>
       </c>
       <c r="H35">
-        <v>1.428571428571429</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="I35">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J35">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K35">
         <v>0.6000000000000001</v>
@@ -1781,7 +1871,7 @@
         <v>2015</v>
       </c>
       <c r="O35">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="36">
@@ -1839,11 +1929,17 @@
           <t>CMR</t>
         </is>
       </c>
+      <c r="H37">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I37">
         <v>2024</v>
       </c>
       <c r="J37">
-        <v>0.2967887173982172</v>
+        <v>0.3</v>
+      </c>
+      <c r="K37">
+        <v>0.4</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -1854,6 +1950,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N37">
+        <v>2015</v>
+      </c>
+      <c r="O37">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1876,13 +1978,13 @@
         </is>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I38">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J38">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K38">
         <v>0.5</v>
@@ -1901,7 +2003,7 @@
         <v>2015</v>
       </c>
       <c r="O38">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="39">
@@ -1924,13 +2026,13 @@
         </is>
       </c>
       <c r="H39">
-        <v>-2.857142857142857</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I39">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J39">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K39">
         <v>0.5</v>
@@ -1949,7 +2051,7 @@
         <v>2015</v>
       </c>
       <c r="O39">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="40">
@@ -2371,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J51">
         <v>0.4</v>
@@ -2392,6 +2494,9 @@
       <c r="N51">
         <v>2015</v>
       </c>
+      <c r="O51">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2412,11 +2517,17 @@
           <t>ECU</t>
         </is>
       </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
       <c r="I52">
         <v>2024</v>
       </c>
       <c r="J52">
-        <v>0.3023016914532661</v>
+        <v>0.3</v>
+      </c>
+      <c r="K52">
+        <v>0.3</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2427,6 +2538,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N52">
+        <v>2015</v>
       </c>
     </row>
     <row r="53">
@@ -2520,11 +2634,17 @@
           <t>EST</t>
         </is>
       </c>
+      <c r="H55">
+        <v>3.333333333333333</v>
+      </c>
       <c r="I55">
         <v>2024</v>
       </c>
       <c r="J55">
-        <v>0.2926458243558249</v>
+        <v>0.3</v>
+      </c>
+      <c r="K55">
+        <v>0.6000000000000001</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -2535,6 +2655,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N55">
+        <v>2015</v>
+      </c>
+      <c r="O55">
+        <v>0.51</v>
       </c>
     </row>
     <row r="56">
@@ -2557,13 +2683,13 @@
         </is>
       </c>
       <c r="H56">
-        <v>2.857142857142857</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I56">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J56">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="K56">
         <v>0.8</v>
@@ -2582,7 +2708,7 @@
         <v>2015</v>
       </c>
       <c r="O56">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -2716,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J60">
         <v>0.5</v>
@@ -2738,7 +2864,7 @@
         <v>2015</v>
       </c>
       <c r="O60">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="61">
@@ -2764,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J61">
         <v>0.5</v>
@@ -2786,7 +2912,7 @@
         <v>2015</v>
       </c>
       <c r="O61">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="62">
@@ -2917,10 +3043,10 @@
         </is>
       </c>
       <c r="H65">
-        <v>2.857142857142857</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="I65">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J65">
         <v>0.6000000000000001</v>
@@ -2942,7 +3068,7 @@
         <v>2015</v>
       </c>
       <c r="O65">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2964,11 +3090,17 @@
           <t>GMB</t>
         </is>
       </c>
+      <c r="H66">
+        <v>2.222222222222222</v>
+      </c>
       <c r="I66">
         <v>2024</v>
       </c>
       <c r="J66">
-        <v>0.2666138451283817</v>
+        <v>0.3</v>
+      </c>
+      <c r="K66">
+        <v>0.5</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -2979,6 +3111,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N66">
+        <v>2015</v>
+      </c>
+      <c r="O66">
+        <v>0.41</v>
       </c>
     </row>
     <row r="67">
@@ -3001,13 +3139,13 @@
         </is>
       </c>
       <c r="H67">
-        <v>2.857142857142857</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I67">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J67">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="K67">
         <v>0.8</v>
@@ -3026,7 +3164,7 @@
         <v>2015</v>
       </c>
       <c r="O67">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -3052,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J68">
         <v>0.4</v>
@@ -3073,6 +3211,9 @@
       <c r="N68">
         <v>2015</v>
       </c>
+      <c r="O68">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3277,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J74">
         <v>0.4</v>
@@ -3298,6 +3439,9 @@
       <c r="N74">
         <v>2015</v>
       </c>
+      <c r="O74">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3358,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J76">
         <v>0.4</v>
@@ -3379,6 +3523,9 @@
       <c r="N76">
         <v>2015</v>
       </c>
+      <c r="O76">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3435,11 +3582,17 @@
           <t>IDN</t>
         </is>
       </c>
+      <c r="H78">
+        <v>-1.111111111111111</v>
+      </c>
       <c r="I78">
         <v>2024</v>
       </c>
       <c r="J78">
-        <v>0.3534693612422131</v>
+        <v>0.4</v>
+      </c>
+      <c r="K78">
+        <v>0.3</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -3450,6 +3603,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N78">
+        <v>2015</v>
       </c>
     </row>
     <row r="79">
@@ -3471,11 +3627,17 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="H79">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I79">
         <v>2024</v>
       </c>
       <c r="J79">
-        <v>0.3229123989071377</v>
+        <v>0.3</v>
+      </c>
+      <c r="K79">
+        <v>0.4</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -3486,6 +3648,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N79">
+        <v>2015</v>
+      </c>
+      <c r="O79">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3544,13 +3712,13 @@
         </is>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I81">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J81">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K81">
         <v>0.7000000000000001</v>
@@ -3569,7 +3737,7 @@
         <v>2015</v>
       </c>
       <c r="O81">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3592,10 +3760,10 @@
         </is>
       </c>
       <c r="H82">
-        <v>-1.428571428571429</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I82">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J82">
         <v>0.6000000000000001</v>
@@ -3617,7 +3785,7 @@
         <v>2015</v>
       </c>
       <c r="O82">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="83">
@@ -3747,11 +3915,17 @@
           <t>JAM</t>
         </is>
       </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
       <c r="I86">
         <v>2024</v>
       </c>
       <c r="J86">
-        <v>0.2574774550948548</v>
+        <v>0.3</v>
+      </c>
+      <c r="K86">
+        <v>0.3</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -3762,6 +3936,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N86">
+        <v>2015</v>
       </c>
     </row>
     <row r="87">
@@ -3783,11 +3960,17 @@
           <t>JOR</t>
         </is>
       </c>
+      <c r="H87">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I87">
         <v>2024</v>
       </c>
       <c r="J87">
-        <v>0.3000374359700755</v>
+        <v>0.3</v>
+      </c>
+      <c r="K87">
+        <v>0.4</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -3798,6 +3981,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N87">
+        <v>2015</v>
+      </c>
+      <c r="O87">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3856,13 +4045,13 @@
         </is>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I89">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J89">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K89">
         <v>0.5</v>
@@ -3881,7 +4070,7 @@
         <v>2015</v>
       </c>
       <c r="O89">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="90">
@@ -3903,11 +4092,17 @@
           <t>KEN</t>
         </is>
       </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
       <c r="I90">
         <v>2024</v>
       </c>
       <c r="J90">
-        <v>0.3031571598783817</v>
+        <v>0.3</v>
+      </c>
+      <c r="K90">
+        <v>0.3</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -3918,6 +4113,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N90">
+        <v>2015</v>
       </c>
     </row>
     <row r="91">
@@ -3940,13 +4138,13 @@
         </is>
       </c>
       <c r="H91">
-        <v>1.428571428571429</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="I91">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J91">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K91">
         <v>0.6000000000000001</v>
@@ -3965,7 +4163,7 @@
         <v>2015</v>
       </c>
       <c r="O91">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="92">
@@ -3988,10 +4186,10 @@
         </is>
       </c>
       <c r="H92">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I92">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J92">
         <v>0.4</v>
@@ -4013,7 +4211,7 @@
         <v>2015</v>
       </c>
       <c r="O92">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="93">
@@ -4107,11 +4305,17 @@
           <t>KOR</t>
         </is>
       </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
       <c r="I95">
         <v>2024</v>
       </c>
       <c r="J95">
-        <v>0.2506902562716818</v>
+        <v>0.3</v>
+      </c>
+      <c r="K95">
+        <v>0.3</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4122,6 +4326,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N95">
+        <v>2015</v>
       </c>
     </row>
     <row r="96">
@@ -4144,13 +4351,13 @@
         </is>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I96">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J96">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K96">
         <v>0.7000000000000001</v>
@@ -4169,7 +4376,7 @@
         <v>2015</v>
       </c>
       <c r="O96">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -4192,10 +4399,10 @@
         </is>
       </c>
       <c r="H97">
-        <v>-1.428571428571429</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I97">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J97">
         <v>0.6000000000000001</v>
@@ -4217,7 +4424,7 @@
         <v>2015</v>
       </c>
       <c r="O97">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="98">
@@ -4239,11 +4446,17 @@
           <t>LBN</t>
         </is>
       </c>
+      <c r="H98">
+        <v>-1.25</v>
+      </c>
       <c r="I98">
         <v>2023</v>
       </c>
       <c r="J98">
-        <v>0.4372070724474146</v>
+        <v>0.4</v>
+      </c>
+      <c r="K98">
+        <v>0.3</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4254,6 +4467,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N98">
+        <v>2015</v>
       </c>
     </row>
     <row r="99">
@@ -4276,13 +4492,13 @@
         </is>
       </c>
       <c r="H99">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I99">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J99">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K99">
         <v>0.4</v>
@@ -4300,6 +4516,9 @@
       <c r="N99">
         <v>2015</v>
       </c>
+      <c r="O99">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4321,10 +4540,10 @@
         </is>
       </c>
       <c r="H100">
-        <v>-2.142857142857143</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="I100">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J100">
         <v>1.2</v>
@@ -4346,7 +4565,7 @@
         <v>2015</v>
       </c>
       <c r="O100">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="101">
@@ -4444,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J103">
         <v>0.7000000000000001</v>
@@ -4466,7 +4685,7 @@
         <v>2015</v>
       </c>
       <c r="O103">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -4632,11 +4851,17 @@
           <t>MAR</t>
         </is>
       </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
       <c r="I108">
         <v>2024</v>
       </c>
       <c r="J108">
-        <v>0.3181170621607834</v>
+        <v>0.3</v>
+      </c>
+      <c r="K108">
+        <v>0.3</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -4647,6 +4872,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N108">
+        <v>2015</v>
       </c>
     </row>
     <row r="109">
@@ -4705,13 +4933,13 @@
         </is>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I110">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J110">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="K110">
         <v>0.8</v>
@@ -4730,7 +4958,7 @@
         <v>2015</v>
       </c>
       <c r="O110">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -4788,11 +5016,17 @@
           <t>MEX</t>
         </is>
       </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
       <c r="I112">
         <v>2024</v>
       </c>
       <c r="J112">
-        <v>0.2513758052807409</v>
+        <v>0.3</v>
+      </c>
+      <c r="K112">
+        <v>0.3</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -4803,6 +5037,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N112">
+        <v>2015</v>
       </c>
     </row>
     <row r="113">
@@ -4825,13 +5062,13 @@
         </is>
       </c>
       <c r="H113">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="I113">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J113">
-        <v>0.6000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="K113">
         <v>0.7000000000000001</v>
@@ -4850,7 +5087,7 @@
         <v>2015</v>
       </c>
       <c r="O113">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -4909,10 +5146,10 @@
         </is>
       </c>
       <c r="H115">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I115">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J115">
         <v>0.7000000000000001</v>
@@ -4934,7 +5171,7 @@
         <v>2015</v>
       </c>
       <c r="O115">
-        <v>0.7300000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -4996,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J117">
         <v>0.4</v>
@@ -5017,6 +5254,9 @@
       <c r="N117">
         <v>2015</v>
       </c>
+      <c r="O117">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5074,10 +5314,10 @@
         </is>
       </c>
       <c r="H119">
-        <v>-0.8333333333333337</v>
+        <v>-0.6481481481481484</v>
       </c>
       <c r="I119">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J119">
         <v>1.7</v>
@@ -5099,7 +5339,7 @@
         <v>2015</v>
       </c>
       <c r="O119">
-        <v>1.290000000000002</v>
+        <v>1.230000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -5122,13 +5362,13 @@
         </is>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I120">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K120">
         <v>1</v>
@@ -5147,7 +5387,7 @@
         <v>2015</v>
       </c>
       <c r="O120">
-        <v>0.86</v>
+        <v>0.8200000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -5170,13 +5410,13 @@
         </is>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I121">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J121">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="K121">
         <v>0.6000000000000001</v>
@@ -5195,7 +5435,7 @@
         <v>2015</v>
       </c>
       <c r="O121">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="122">
@@ -5254,10 +5494,10 @@
         </is>
       </c>
       <c r="H123">
-        <v>-1.428571428571429</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I123">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J123">
         <v>0.5</v>
@@ -5278,6 +5518,9 @@
       <c r="N123">
         <v>2015</v>
       </c>
+      <c r="O123">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5298,11 +5541,17 @@
           <t>MYS</t>
         </is>
       </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
       <c r="I124">
         <v>2024</v>
       </c>
       <c r="J124">
-        <v>0.3033565877707891</v>
+        <v>0.3</v>
+      </c>
+      <c r="K124">
+        <v>0.3</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -5313,6 +5562,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N124">
+        <v>2015</v>
       </c>
     </row>
     <row r="125">
@@ -5335,10 +5587,10 @@
         </is>
       </c>
       <c r="H125">
-        <v>-1.428571428571429</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I125">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J125">
         <v>0.5</v>
@@ -5359,6 +5611,9 @@
       <c r="N125">
         <v>2015</v>
       </c>
+      <c r="O125">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5380,10 +5635,10 @@
         </is>
       </c>
       <c r="H126">
-        <v>0.7142857142857143</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I126">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -5405,7 +5660,7 @@
         <v>2015</v>
       </c>
       <c r="O126">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="127">
@@ -5467,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J128">
         <v>0.4</v>
@@ -5488,6 +5743,9 @@
       <c r="N128">
         <v>2015</v>
       </c>
+      <c r="O128">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5580,11 +5838,17 @@
           <t>NPL</t>
         </is>
       </c>
+      <c r="H131">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I131">
         <v>2024</v>
       </c>
       <c r="J131">
-        <v>0.3341276401359178</v>
+        <v>0.3</v>
+      </c>
+      <c r="K131">
+        <v>0.4</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -5595,6 +5859,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N131">
+        <v>2015</v>
+      </c>
+      <c r="O131">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -5617,10 +5887,10 @@
         </is>
       </c>
       <c r="H132">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I132">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J132">
         <v>0.4</v>
@@ -5642,7 +5912,7 @@
         <v>2015</v>
       </c>
       <c r="O132">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="133">
@@ -5664,11 +5934,17 @@
           <t>NZL</t>
         </is>
       </c>
+      <c r="H133">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I133">
         <v>2024</v>
       </c>
       <c r="J133">
-        <v>0.3336795257293529</v>
+        <v>0.3</v>
+      </c>
+      <c r="K133">
+        <v>0.4</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -5679,6 +5955,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N133">
+        <v>2015</v>
+      </c>
+      <c r="O133">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -5704,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J134">
         <v>0.6000000000000001</v>
@@ -5726,7 +6008,7 @@
         <v>2015</v>
       </c>
       <c r="O134">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="135">
@@ -5752,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J135">
         <v>0.4</v>
@@ -5773,6 +6055,9 @@
       <c r="N135">
         <v>2015</v>
       </c>
+      <c r="O135">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5902,10 +6187,10 @@
         </is>
       </c>
       <c r="H139">
-        <v>-2.857142857142857</v>
+        <v>-2.5</v>
       </c>
       <c r="I139">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J139">
         <v>1</v>
@@ -5927,7 +6212,7 @@
         <v>2015</v>
       </c>
       <c r="O139">
-        <v>0.6300000000000001</v>
+        <v>0.6200000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -5949,11 +6234,17 @@
           <t>PNG</t>
         </is>
       </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
       <c r="I140">
         <v>2024</v>
       </c>
       <c r="J140">
-        <v>0.2998393123535542</v>
+        <v>0.3</v>
+      </c>
+      <c r="K140">
+        <v>0.3</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -5964,6 +6255,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N140">
+        <v>2015</v>
       </c>
     </row>
     <row r="141">
@@ -6058,10 +6352,10 @@
         </is>
       </c>
       <c r="H143">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I143">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J143">
         <v>0.4</v>
@@ -6083,7 +6377,7 @@
         <v>2015</v>
       </c>
       <c r="O143">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="144">
@@ -6106,10 +6400,10 @@
         </is>
       </c>
       <c r="H144">
-        <v>-1.428571428571429</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="I144">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J144">
         <v>0.5</v>
@@ -6130,6 +6424,9 @@
       <c r="N144">
         <v>2015</v>
       </c>
+      <c r="O144">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6190,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J146">
         <v>0.5</v>
@@ -6212,7 +6509,7 @@
         <v>2015</v>
       </c>
       <c r="O146">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="147">
@@ -6271,10 +6568,10 @@
         </is>
       </c>
       <c r="H148">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I148">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J148">
         <v>0.4</v>
@@ -6296,7 +6593,7 @@
         <v>2015</v>
       </c>
       <c r="O148">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="149">
@@ -6319,13 +6616,13 @@
         </is>
       </c>
       <c r="H149">
-        <v>-1.428571428571429</v>
+        <v>-3.703703703703703</v>
       </c>
       <c r="I149">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J149">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="K149">
         <v>0.7000000000000001</v>
@@ -6344,7 +6641,7 @@
         <v>2015</v>
       </c>
       <c r="O149">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="150">
@@ -6367,10 +6664,10 @@
         </is>
       </c>
       <c r="H150">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I150">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J150">
         <v>0.4</v>
@@ -6392,7 +6689,7 @@
         <v>2015</v>
       </c>
       <c r="O150">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="151">
@@ -6450,11 +6747,17 @@
           <t>SLB</t>
         </is>
       </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
       <c r="I152">
         <v>2024</v>
       </c>
       <c r="J152">
-        <v>0.3210953765687003</v>
+        <v>0.3</v>
+      </c>
+      <c r="K152">
+        <v>0.3</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -6465,6 +6768,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N152">
+        <v>2015</v>
       </c>
     </row>
     <row r="153">
@@ -6486,11 +6792,17 @@
           <t>SLE</t>
         </is>
       </c>
+      <c r="H153">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I153">
         <v>2024</v>
       </c>
       <c r="J153">
-        <v>0.3136718677440243</v>
+        <v>0.3</v>
+      </c>
+      <c r="K153">
+        <v>0.4</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -6501,6 +6813,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N153">
+        <v>2015</v>
+      </c>
+      <c r="O153">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="154">
@@ -6595,13 +6913,13 @@
         </is>
       </c>
       <c r="H156">
-        <v>1.309523809523809</v>
+        <v>1.388888888888888</v>
       </c>
       <c r="I156">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J156">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K156">
         <v>1.7</v>
@@ -6620,7 +6938,7 @@
         <v>2015</v>
       </c>
       <c r="O156">
-        <v>1.464999999999999</v>
+        <v>1.405000000000002</v>
       </c>
     </row>
     <row r="157">
@@ -6643,10 +6961,10 @@
         </is>
       </c>
       <c r="H157">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I157">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J157">
         <v>0.4</v>
@@ -6668,7 +6986,7 @@
         <v>2015</v>
       </c>
       <c r="O157">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="158">
@@ -6726,11 +7044,17 @@
           <t>SUR</t>
         </is>
       </c>
+      <c r="H159">
+        <v>-1.111111111111111</v>
+      </c>
       <c r="I159">
         <v>2024</v>
       </c>
       <c r="J159">
-        <v>0.3887303774736643</v>
+        <v>0.4</v>
+      </c>
+      <c r="K159">
+        <v>0.3</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -6741,6 +7065,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N159">
+        <v>2015</v>
       </c>
     </row>
     <row r="160">
@@ -6967,6 +7294,9 @@
       <c r="N165">
         <v>2015</v>
       </c>
+      <c r="O165">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6987,11 +7317,17 @@
           <t>TCA</t>
         </is>
       </c>
+      <c r="H166">
+        <v>2.222222222222222</v>
+      </c>
       <c r="I166">
         <v>2024</v>
       </c>
       <c r="J166">
-        <v>0.2535672926851991</v>
+        <v>0.3</v>
+      </c>
+      <c r="K166">
+        <v>0.5</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -7002,6 +7338,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N166">
+        <v>2015</v>
+      </c>
+      <c r="O166">
+        <v>0.41</v>
       </c>
     </row>
     <row r="167">
@@ -7024,10 +7366,10 @@
         </is>
       </c>
       <c r="H167">
-        <v>-1.571428571428571</v>
+        <v>-1.277777777777778</v>
       </c>
       <c r="I167">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J167">
         <v>2.2</v>
@@ -7049,7 +7391,7 @@
         <v>2015</v>
       </c>
       <c r="O167">
-        <v>1.464999999999999</v>
+        <v>1.405000000000002</v>
       </c>
     </row>
     <row r="168">
@@ -7072,13 +7414,13 @@
         </is>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I168">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J168">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K168">
         <v>0.5</v>
@@ -7097,7 +7439,7 @@
         <v>2015</v>
       </c>
       <c r="O168">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="169">
@@ -7119,11 +7461,17 @@
           <t>THA</t>
         </is>
       </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
       <c r="I169">
         <v>2024</v>
       </c>
       <c r="J169">
-        <v>0.2939475148473389</v>
+        <v>0.3</v>
+      </c>
+      <c r="K169">
+        <v>0.3</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -7134,6 +7482,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N169">
+        <v>2015</v>
       </c>
     </row>
     <row r="170">
@@ -7156,10 +7507,10 @@
         </is>
       </c>
       <c r="H170">
-        <v>2.857142857142857</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="I170">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J170">
         <v>0.4</v>
@@ -7181,7 +7532,7 @@
         <v>2015</v>
       </c>
       <c r="O170">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="171">
@@ -7204,13 +7555,13 @@
         </is>
       </c>
       <c r="H171">
-        <v>2.857142857142857</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="I171">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J171">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K171">
         <v>1.2</v>
@@ -7229,7 +7580,7 @@
         <v>2015</v>
       </c>
       <c r="O171">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="172">
@@ -7251,11 +7602,17 @@
           <t>TLS</t>
         </is>
       </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
       <c r="I172">
         <v>2024</v>
       </c>
       <c r="J172">
-        <v>0.3779939192520708</v>
+        <v>0.4</v>
+      </c>
+      <c r="K172">
+        <v>0.4</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -7266,6 +7623,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N172">
+        <v>2015</v>
+      </c>
+      <c r="O172">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -7291,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J173">
         <v>0.4</v>
@@ -7312,6 +7675,9 @@
       <c r="N173">
         <v>2015</v>
       </c>
+      <c r="O173">
+        <v>0.3200000000000001</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7333,13 +7699,13 @@
         </is>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I174">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J174">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K174">
         <v>1.2</v>
@@ -7358,7 +7724,7 @@
         <v>2015</v>
       </c>
       <c r="O174">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="175">
@@ -7380,11 +7746,17 @@
           <t>TUN</t>
         </is>
       </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
       <c r="I175">
         <v>2024</v>
       </c>
       <c r="J175">
-        <v>0.3168853989539216</v>
+        <v>0.3</v>
+      </c>
+      <c r="K175">
+        <v>0.3</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -7395,6 +7767,9 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N175">
+        <v>2015</v>
       </c>
     </row>
     <row r="176">
@@ -7453,13 +7828,13 @@
         </is>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="I177">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J177">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K177">
         <v>0.4</v>
@@ -7477,6 +7852,9 @@
       <c r="N177">
         <v>2015</v>
       </c>
+      <c r="O177">
+        <v>0.3200000000000001</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7498,10 +7876,10 @@
         </is>
       </c>
       <c r="H178">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I178">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J178">
         <v>0.4</v>
@@ -7523,7 +7901,7 @@
         <v>2015</v>
       </c>
       <c r="O178">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="179">
@@ -7546,10 +7924,10 @@
         </is>
       </c>
       <c r="H179">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I179">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J179">
         <v>0.4</v>
@@ -7571,7 +7949,7 @@
         <v>2015</v>
       </c>
       <c r="O179">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="180">
@@ -7593,11 +7971,17 @@
           <t>UKR</t>
         </is>
       </c>
+      <c r="H180">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I180">
         <v>2024</v>
       </c>
       <c r="J180">
-        <v>0.2929404927581373</v>
+        <v>0.3</v>
+      </c>
+      <c r="K180">
+        <v>0.4</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -7608,6 +7992,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N180">
+        <v>2015</v>
+      </c>
+      <c r="O180">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -7633,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J181">
         <v>0.4</v>
@@ -7654,6 +8044,9 @@
       <c r="N181">
         <v>2015</v>
       </c>
+      <c r="O181">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7711,10 +8104,10 @@
         </is>
       </c>
       <c r="H183">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I183">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J183">
         <v>0.6000000000000001</v>
@@ -7736,7 +8129,7 @@
         <v>2015</v>
       </c>
       <c r="O183">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="184">
@@ -7798,7 +8191,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J185">
         <v>0.4</v>
@@ -7819,6 +8212,9 @@
       <c r="N185">
         <v>2015</v>
       </c>
+      <c r="O185">
+        <v>0.3100000000000001</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7840,10 +8236,10 @@
         </is>
       </c>
       <c r="H186">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I186">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J186">
         <v>0.6000000000000001</v>
@@ -7865,7 +8261,7 @@
         <v>2015</v>
       </c>
       <c r="O186">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -7887,11 +8283,17 @@
           <t>WSM</t>
         </is>
       </c>
+      <c r="H187">
+        <v>1.111111111111111</v>
+      </c>
       <c r="I187">
         <v>2024</v>
       </c>
       <c r="J187">
-        <v>0.2846489342577997</v>
+        <v>0.3</v>
+      </c>
+      <c r="K187">
+        <v>0.4</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -7902,6 +8304,12 @@
         <is>
           <t>Carbon intensity of GDP (kg CO2e per 2021 PPP $ of GDP)</t>
         </is>
+      </c>
+      <c r="N187">
+        <v>2015</v>
+      </c>
+      <c r="O187">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -7924,10 +8332,10 @@
         </is>
       </c>
       <c r="H188">
-        <v>1.428571428571429</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I188">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J188">
         <v>0.6000000000000001</v>
@@ -7949,7 +8357,7 @@
         <v>2015</v>
       </c>
       <c r="O188">
-        <v>0.6300000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -7975,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J189">
         <v>0.6000000000000001</v>
@@ -7997,7 +8405,7 @@
         <v>2015</v>
       </c>
       <c r="O189">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="190">
@@ -8020,13 +8428,13 @@
         </is>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="I190">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J190">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K190">
         <v>0.4</v>
@@ -8043,6 +8451,9 @@
       </c>
       <c r="N190">
         <v>2015</v>
+      </c>
+      <c r="O190">
+        <v>0.3100000000000001</v>
       </c>
     </row>
     <row r="191">
